--- a/sheets/대금율보/검수/단오노래.xlsx
+++ b/sheets/대금율보/검수/단오노래.xlsx
@@ -5757,7 +5757,7 @@
       </c>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –淋
 潕</t>
         </is>
@@ -5795,7 +5795,7 @@
         <is>
           <t xml:space="preserve">潢潢
 南∧
-林‹</t>
+林</t>
         </is>
       </c>
       <c r="Q4" s="25" t="inlineStr">
@@ -5957,7 +5957,7 @@
         <is>
           <t xml:space="preserve">林
 太⌇
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -5967,8 +5967,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="E6" s="27" t="inlineStr">
@@ -5978,8 +5977,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="G6" s="27" t="inlineStr">
@@ -5989,8 +5987,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="I6" s="27" t="inlineStr">
@@ -6002,7 +5999,7 @@
         <is>
           <t xml:space="preserve">林
 南∧
-林‹</t>
+林</t>
         </is>
       </c>
       <c r="K6" s="27" t="inlineStr">
@@ -6014,7 +6011,7 @@
         <is>
           <t xml:space="preserve">潢·
 潢
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="M6" s="27" t="inlineStr">
@@ -6024,8 +6021,7 @@
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="O6" s="27" t="inlineStr">
@@ -6037,7 +6033,7 @@
         <is>
           <t xml:space="preserve">汰南∧
 南汰
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="Q6" s="27" t="inlineStr">
@@ -6047,8 +6043,7 @@
       </c>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="S6" s="27" t="inlineStr">
@@ -6059,8 +6054,7 @@
       <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰⌇
-汰淋
-‹</t>
+汰淋</t>
         </is>
       </c>
       <c r="U6" s="27" t="inlineStr">
@@ -6262,7 +6256,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 汰
 –潢</t>
         </is>
@@ -6336,7 +6330,7 @@
         <is>
           <t xml:space="preserve">–
 汰汰
-南∧‹</t>
+南∧</t>
         </is>
       </c>
       <c r="U10" s="25" t="inlineStr">
@@ -6463,14 +6457,13 @@
           <t xml:space="preserve">⌇
 –
 –
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -6482,7 +6475,7 @@
         <is>
           <t xml:space="preserve">汰
 林
-太‹</t>
+太</t>
         </is>
       </c>
       <c r="G12" s="27" t="inlineStr">
@@ -6492,8 +6485,7 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太⌇
-‹</t>
+          <t xml:space="preserve">太⌇</t>
         </is>
       </c>
       <c r="I12" s="27" t="inlineStr">
@@ -6503,8 +6495,7 @@
       </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧
-‹</t>
+          <t xml:space="preserve">南∧</t>
         </is>
       </c>
       <c r="K12" s="27" t="inlineStr">
@@ -6514,8 +6505,7 @@
       </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="M12" s="27" t="inlineStr">
@@ -6527,7 +6517,7 @@
         <is>
           <t xml:space="preserve">汰
 林
-太‹</t>
+太</t>
         </is>
       </c>
       <c r="O12" s="27" t="inlineStr">
@@ -6537,7 +6527,7 @@
       </c>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧‹</t>
+          <t xml:space="preserve">南∧</t>
         </is>
       </c>
       <c r="Q12" s="27" t="inlineStr">
@@ -6550,14 +6540,13 @@
           <t xml:space="preserve">⌇
 –
 –
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="S12" s="28"/>
       <c r="T12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="U12" s="27" t="inlineStr">
@@ -6942,7 +6931,7 @@
       </c>
       <c r="T17" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?
+          <t xml:space="preserve">汰
 –淋
 淋</t>
         </is>
@@ -6959,14 +6948,13 @@
         <is>
           <t xml:space="preserve">林·
 林
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
@@ -6978,7 +6966,7 @@
         <is>
           <t xml:space="preserve">林
 太⌇
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="G18" s="27" t="inlineStr">
@@ -6990,7 +6978,7 @@
         <is>
           <t xml:space="preserve">林·
 太⌇
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="I18" s="27" t="inlineStr">
@@ -7002,7 +6990,7 @@
         <is>
           <t xml:space="preserve">汰
 汰
-南∧‹</t>
+南∧</t>
         </is>
       </c>
       <c r="K18" s="27" t="inlineStr">
@@ -7014,7 +7002,7 @@
         <is>
           <t xml:space="preserve">–
 –
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="M18" s="27"/>
@@ -7022,14 +7010,13 @@
         <is>
           <t xml:space="preserve">–
 –
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="O18" s="27"/>
       <c r="P18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="Q18" s="27" t="inlineStr">
@@ -7041,7 +7028,7 @@
         <is>
           <t xml:space="preserve">汰
 林
-太‹</t>
+太</t>
         </is>
       </c>
       <c r="S18" s="27" t="inlineStr">
@@ -7051,8 +7038,7 @@
       </c>
       <c r="T18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋⌇
-‹</t>
+          <t xml:space="preserve">淋⌇</t>
         </is>
       </c>
       <c r="U18" s="27" t="inlineStr">

--- a/sheets/대금율보/검수/단오노래.xlsx
+++ b/sheets/대금율보/검수/단오노래.xlsx
@@ -5532,32 +5532,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="18.03" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="114.29" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="511.6" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="511.6" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="511.6" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="511.6" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="6.0" customHeight="true">
       <c r="A7" s="0"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="114.29" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="20" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
       <c r="T8" s="20"/>
       <c r="U8" s="20"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="511.6" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="511.6" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="511.6" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="25"/>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="511.6" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="6.0" customHeight="true">
       <c r="A13" s="0"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="114.29" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="20" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       <c r="T14" s="20"/>
       <c r="U14" s="20"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="511.6" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="511.6" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="511.6" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="511.6" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="35"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="6" max="16383" man="1"/>
     <brk id="12" max="16383" man="1"/>
